--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0252FA02-8B08-4FD4-8037-C9706421A78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial" sheetId="3" r:id="rId1"/>
@@ -68,17 +74,6 @@
     <t>手引き</t>
   </si>
   <si>
-    <t>◇ゲームの目的
-Normは全6層からなるステージをクリアすることが目的です。
-マスを選択してステージを進め、各階層にいるボスを討伐することで次の階層に進めます。
-「探索」を選んでマスを選択してみましょう。
-※この内容はサイドメニューの「ヘルプ」コマンドで確認することができます。</t>
-  </si>
-  <si>
-    <t>「探索」からマス選択することができます。
-マスの種類はバトルとそれ以外に分けられます。</t>
-  </si>
-  <si>
     <t>■マス選択
 バトルマスはメンバーを選んで敵とバトルを行います。</t>
   </si>
@@ -223,18 +218,95 @@
 Passive・Unique魔法は作戦に設定しなくても発動しますが
 条件を設定した時は条件に一致する場合にのみ効果を発動します。</t>
   </si>
+  <si>
+    <t>◇ゲームの流れ
+「Norm」はステージに配置されたボスを倒すことが目的のシミュレーションRPGです。
+味方ユニットを出撃させバトルを行い敵ユニットを討伐することができます。
+拠点を選択し「出撃」コマンドを選んで味方ユニットを出撃させてみましょう。
+※この内容は「ヘルプ」コマンドで確認することができます。</t>
+    <rPh sb="5" eb="6">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>シュツゲキ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>キョテン</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>シュツゲキ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>シュツゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味方ユニットの「出撃」「移動」にはコマンドポイントを1消費します。
+コマンドポイントは所有している拠点の数だけ保有し
+「ターン開始」時に最大まで回復します。</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュツゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ショユウ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ホユウ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,345 +315,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -589,323 +346,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1163,49 +631,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="5.63636363636364" customWidth="1"/>
-    <col min="4" max="6" width="7.81818181818182" customWidth="1"/>
+    <col min="3" max="3" width="5.6328125" customWidth="1"/>
+    <col min="4" max="6" width="7.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1221,12 +689,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1265,18 +733,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1285,31 +753,31 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>320</v>
+        <v>-120</v>
       </c>
       <c r="H3">
-        <v>-272</v>
+        <v>-280</v>
       </c>
       <c r="I3">
-        <v>184</v>
+        <v>400</v>
       </c>
       <c r="J3">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="K3">
-        <v>320</v>
+        <v>-80</v>
       </c>
       <c r="L3">
-        <v>-160</v>
+        <v>-120</v>
       </c>
       <c r="M3">
-        <v>496</v>
+        <v>640</v>
       </c>
       <c r="N3">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -1353,7 +821,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -1397,7 +865,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -1441,7 +909,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2000</v>
       </c>
@@ -1485,12 +953,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3000</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1529,12 +997,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3010</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1573,12 +1041,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3020</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1617,7 +1085,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4000</v>
       </c>
@@ -1661,7 +1129,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>4010</v>
       </c>
@@ -1705,7 +1173,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5000</v>
       </c>
@@ -1749,7 +1217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5010</v>
       </c>
@@ -1793,7 +1261,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5020</v>
       </c>
@@ -1837,7 +1305,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>6000</v>
       </c>
@@ -1881,7 +1349,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>6010</v>
       </c>
@@ -1925,12 +1393,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>7000</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1969,12 +1437,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>7010</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2013,7 +1481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>8000</v>
       </c>
@@ -2057,7 +1525,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>9000</v>
       </c>
@@ -2101,7 +1569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>9010</v>
       </c>
@@ -2145,7 +1613,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10000</v>
       </c>
@@ -2189,7 +1657,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>11000</v>
       </c>
@@ -2233,7 +1701,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>11010</v>
       </c>
@@ -2277,7 +1745,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>11020</v>
       </c>
@@ -2322,22 +1790,21 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="62.8181818181818" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="62.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2348,29 +1815,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="130" spans="1:3">
+    <row r="2" spans="1:3" ht="117" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="26" spans="1:3">
+      <c r="C2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" ht="26" spans="1:3">
+      <c r="C3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -2378,10 +1845,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="26" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -2389,10 +1856,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -2400,231 +1867,231 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="52" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="52" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2000</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" ht="26" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3000</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" ht="39" spans="1:3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3010</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" ht="26" spans="1:3">
+    </row>
+    <row r="10" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3020</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" ht="26" spans="1:3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4000</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" ht="39" spans="1:3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>4010</v>
       </c>
       <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="26" spans="1:3">
+    </row>
+    <row r="13" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5000</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" ht="26" spans="1:3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5010</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" ht="26" spans="1:3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5020</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" ht="26" spans="1:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>6000</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" ht="52" spans="1:3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="52" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>6010</v>
       </c>
       <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" ht="39" spans="1:3">
+    </row>
+    <row r="18" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>7000</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" ht="65" spans="1:3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="65" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>7010</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" ht="26" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>8000</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" ht="52" spans="1:3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="52" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>9000</v>
       </c>
       <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" ht="26" spans="1:3">
+    </row>
+    <row r="22" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>9010</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" ht="39" spans="1:3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10000</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" ht="39" spans="1:3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>11000</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" ht="65" spans="1:3">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="65" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>11010</v>
       </c>
       <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" ht="52" spans="1:3">
+    </row>
+    <row r="26" spans="1:3" ht="52" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>11020</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0252FA02-8B08-4FD4-8037-C9706421A78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB2B258-B749-4263-8206-6B74473C9CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>Id</t>
   </si>
@@ -72,14 +72,6 @@
   </si>
   <si>
     <t>手引き</t>
-  </si>
-  <si>
-    <t>■マス選択
-バトルマスはメンバーを選んで敵とバトルを行います。</t>
-  </si>
-  <si>
-    <t>■編成
-バトルに参加するメンバーは最大5名まで編成できます。</t>
   </si>
   <si>
     <t>バトルを開始してみましょう。</t>
@@ -298,6 +290,45 @@
     </rPh>
     <rPh sb="72" eb="74">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>味方ユニットは拠点とその周りに出撃できます。</t>
+    <rPh sb="0" eb="2">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョテン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シュツゲキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出撃した味方ユニットは「移動」コマンドでマスを移動し
+敵ユニットと接触することでバトルすることができます。</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ミカタ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セッショク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -637,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -753,28 +784,28 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>-120</v>
+        <v>-472</v>
       </c>
       <c r="H3">
-        <v>-280</v>
+        <v>176</v>
       </c>
       <c r="I3">
-        <v>400</v>
+        <v>272</v>
       </c>
       <c r="J3">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -782,13 +813,13 @@
         <v>1020</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -797,28 +828,28 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="H4">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="I4">
-        <v>320</v>
+        <v>1040</v>
       </c>
       <c r="J4">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>-108</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -826,13 +857,13 @@
         <v>1030</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -841,28 +872,28 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>-520</v>
+        <v>-160</v>
       </c>
       <c r="H5">
-        <v>112</v>
+        <v>-24</v>
       </c>
       <c r="I5">
-        <v>224</v>
+        <v>360</v>
       </c>
       <c r="J5">
-        <v>112</v>
+        <v>360</v>
       </c>
       <c r="K5">
-        <v>-240</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>-32</v>
+        <v>-160</v>
       </c>
       <c r="M5">
-        <v>584</v>
+        <v>320</v>
       </c>
       <c r="N5">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -870,13 +901,13 @@
         <v>1040</v>
       </c>
       <c r="B6">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -885,42 +916,42 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>504</v>
+        <v>-120</v>
       </c>
       <c r="H6">
-        <v>-272</v>
+        <v>-280</v>
       </c>
       <c r="I6">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J6">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="K6">
-        <v>392</v>
+        <v>-80</v>
       </c>
       <c r="L6">
-        <v>-192</v>
+        <v>-120</v>
       </c>
       <c r="M6">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="N6">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>2000</v>
+        <v>1050</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -929,42 +960,42 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="I7">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="J7">
-        <v>168</v>
+        <v>360</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>3000</v>
+        <v>1060</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -973,16 +1004,16 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-472</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="I8">
-        <v>616</v>
+        <v>272</v>
       </c>
       <c r="J8">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -999,10 +1030,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>3010</v>
+        <v>10040</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1011,95 +1042,95 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>400</v>
+        <v>504</v>
       </c>
       <c r="H9">
-        <v>128</v>
+        <v>-272</v>
       </c>
       <c r="I9">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="J9">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="K9">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="L9">
-        <v>-40</v>
+        <v>-192</v>
       </c>
       <c r="M9">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="N9">
-        <v>116</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>3020</v>
+        <v>2000</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="J10">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="K10">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>-136</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="B11">
         <v>8</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1108,30 +1139,30 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>320</v>
+        <v>616</v>
       </c>
       <c r="J11">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>4010</v>
+        <v>3010</v>
       </c>
       <c r="B12">
         <v>8</v>
@@ -1140,7 +1171,7 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1149,77 +1180,77 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H12">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="I12">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="J12">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="L12">
-        <v>16</v>
+        <v>-40</v>
       </c>
       <c r="M12">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N12">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>5000</v>
+        <v>3020</v>
       </c>
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="D13">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>400</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="I13">
-        <v>540</v>
+        <v>400</v>
       </c>
       <c r="J13">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>-136</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>5010</v>
+        <v>4000</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -1228,183 +1259,183 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>-272</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="I14">
         <v>320</v>
       </c>
       <c r="J14">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="K14">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>16</v>
       </c>
       <c r="M14">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="N14">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>5020</v>
+        <v>4010</v>
       </c>
       <c r="B15">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>-44</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="I15">
-        <v>176</v>
+        <v>320</v>
       </c>
       <c r="J15">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="K15">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>16</v>
       </c>
       <c r="M15">
-        <v>624</v>
+        <v>600</v>
       </c>
       <c r="N15">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>1280</v>
+        <v>540</v>
       </c>
       <c r="J16">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>620</v>
+        <v>410</v>
       </c>
       <c r="G17">
-        <v>500</v>
+        <v>-272</v>
       </c>
       <c r="H17">
+        <v>112</v>
+      </c>
+      <c r="I17">
+        <v>320</v>
+      </c>
+      <c r="J17">
         <v>72</v>
       </c>
-      <c r="I17">
-        <v>280</v>
-      </c>
-      <c r="J17">
-        <v>264</v>
-      </c>
       <c r="K17">
-        <v>400</v>
+        <v>-160</v>
       </c>
       <c r="L17">
-        <v>-144</v>
+        <v>16</v>
       </c>
       <c r="M17">
-        <v>424</v>
+        <v>572</v>
       </c>
       <c r="N17">
-        <v>144</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>7000</v>
+        <v>5020</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1413,130 +1444,130 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I18">
-        <v>640</v>
+        <v>176</v>
       </c>
       <c r="J18">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>7010</v>
+        <v>6000</v>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>600</v>
+      </c>
+      <c r="E19">
         <v>1</v>
       </c>
-      <c r="D19">
-        <v>800</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
       <c r="F19">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="I19">
-        <v>720</v>
+        <v>1280</v>
       </c>
       <c r="J19">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>8000</v>
+        <v>6010</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H20">
-        <v>216</v>
+        <v>72</v>
       </c>
       <c r="I20">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="J20">
+        <v>264</v>
+      </c>
+      <c r="K20">
+        <v>400</v>
+      </c>
+      <c r="L20">
+        <v>-144</v>
+      </c>
+      <c r="M20">
+        <v>424</v>
+      </c>
+      <c r="N20">
         <v>144</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>80</v>
-      </c>
-      <c r="M20">
-        <v>480</v>
-      </c>
-      <c r="N20">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="B21">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1551,10 +1582,10 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>556</v>
+        <v>640</v>
       </c>
       <c r="J21">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1571,16 +1602,16 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>9010</v>
+        <v>7010</v>
       </c>
       <c r="B22">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1589,33 +1620,33 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>160</v>
+        <v>720</v>
       </c>
       <c r="J22">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="K22">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -1624,86 +1655,86 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>320</v>
+        <v>216</v>
       </c>
       <c r="I23">
         <v>320</v>
       </c>
       <c r="J23">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="K23">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="M23">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="N23">
-        <v>144</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>-272</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="J24">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="K24">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>11010</v>
+        <v>9010</v>
       </c>
       <c r="B25">
         <v>200</v>
@@ -1712,51 +1743,51 @@
         <v>2</v>
       </c>
       <c r="D25">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="H25">
-        <v>-272</v>
+        <v>316</v>
       </c>
       <c r="I25">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="J25">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K25">
         <v>320</v>
       </c>
       <c r="L25">
-        <v>-136</v>
+        <v>224</v>
       </c>
       <c r="M25">
-        <v>620</v>
+        <v>540</v>
       </c>
       <c r="N25">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>11020</v>
+        <v>10000</v>
       </c>
       <c r="B26">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1765,27 +1796,159 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H26">
+        <v>320</v>
+      </c>
+      <c r="I26">
+        <v>320</v>
+      </c>
+      <c r="J26">
+        <v>56</v>
+      </c>
+      <c r="K26">
+        <v>320</v>
+      </c>
+      <c r="L26">
+        <v>208</v>
+      </c>
+      <c r="M26">
+        <v>540</v>
+      </c>
+      <c r="N26">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>11000</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>1200</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>504</v>
+      </c>
+      <c r="H27">
+        <v>-272</v>
+      </c>
+      <c r="I27">
+        <v>184</v>
+      </c>
+      <c r="J27">
+        <v>72</v>
+      </c>
+      <c r="K27">
+        <v>320</v>
+      </c>
+      <c r="L27">
+        <v>-160</v>
+      </c>
+      <c r="M27">
+        <v>540</v>
+      </c>
+      <c r="N27">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>11010</v>
+      </c>
+      <c r="B28">
+        <v>200</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>1200</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>504</v>
+      </c>
+      <c r="H28">
+        <v>-272</v>
+      </c>
+      <c r="I28">
+        <v>184</v>
+      </c>
+      <c r="J28">
+        <v>72</v>
+      </c>
+      <c r="K28">
+        <v>320</v>
+      </c>
+      <c r="L28">
+        <v>-136</v>
+      </c>
+      <c r="M28">
+        <v>620</v>
+      </c>
+      <c r="N28">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>11020</v>
+      </c>
+      <c r="B29">
+        <v>111</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>1200</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>156</v>
       </c>
-      <c r="I26">
+      <c r="I29">
         <v>1080</v>
       </c>
-      <c r="J26">
+      <c r="J29">
         <v>256</v>
       </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
         <v>-56</v>
       </c>
-      <c r="M26">
+      <c r="M29">
         <v>648</v>
       </c>
-      <c r="N26">
+      <c r="N29">
         <v>144</v>
       </c>
     </row>
@@ -1797,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.81640625" customWidth="1"/>
@@ -1823,271 +1986,298 @@
         <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1030</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1040</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1050</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1060</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>10040</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2000</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="52" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2000</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="26" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>3000</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="39" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>3010</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="26" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>3020</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>4010</v>
+        <v>3010</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>5000</v>
+        <v>3020</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>5010</v>
+        <v>4000</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="39" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>5020</v>
+        <v>4010</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="26" x14ac:dyDescent="0.2">
       <c r="A16">
+        <v>5000</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5010</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>5020</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>6000</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>6010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="1" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>7000</v>
+      </c>
+      <c r="B21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="52" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>6010</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="39" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>7000</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="22" spans="1:3" ht="65" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>7010</v>
+      </c>
+      <c r="B22" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="65" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>7010</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="23" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>8000</v>
+      </c>
+      <c r="B23" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="26" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>8000</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="24" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>9000</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="1" t="s">
+    </row>
+    <row r="25" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>9010</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="52" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>9000</v>
-      </c>
-      <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="1" t="s">
+    <row r="26" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>10000</v>
+      </c>
+      <c r="B26" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="26" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>9010</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="39" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>10000</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="27" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>11000</v>
+      </c>
+      <c r="B27" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="39" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>11000</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="28" spans="1:3" ht="65" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>11010</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="1" t="s">
+    </row>
+    <row r="29" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>11020</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="65" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>11010</v>
-      </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="52" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>11020</v>
-      </c>
-      <c r="B26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB2B258-B749-4263-8206-6B74473C9CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8410" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial" sheetId="3" r:id="rId1"/>
@@ -21,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -59,12 +53,6 @@
     <t>FocusY</t>
   </si>
   <si>
-    <t>FocusWidth</t>
-  </si>
-  <si>
-    <t>FocusHeight</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -72,6 +60,29 @@
   </si>
   <si>
     <t>手引き</t>
+  </si>
+  <si>
+    <t>◇ゲームの流れ
+このゲームはエインフェリアを育成する3DダンジョンRPGです。
+仲間をダンジョンに出撃させバトルを行いダンジョンボスを討伐しましょう！
+そのためには準備が必要です。
+今いるメインメニュー画面では仲間を増やしたり、アイテムを購入することができます。
+※この内容は「ヘルプ」コマンドで確認することができます。</t>
+  </si>
+  <si>
+    <t>課題に記載された内容をこなしてみましょう！</t>
+  </si>
+  <si>
+    <t>味方ユニットは拠点とその周りに出撃できます。</t>
+  </si>
+  <si>
+    <t>味方ユニットの「出撃」「移動」にはコマンドポイントを1消費します。
+コマンドポイントは所有している拠点の数だけ保有し
+「ターン開始」時に最大まで回復します。</t>
+  </si>
+  <si>
+    <t>出撃した味方ユニットは「移動」コマンドでマスを移動し
+敵ユニットと接触することでバトルすることができます。</t>
   </si>
   <si>
     <t>バトルを開始してみましょう。</t>
@@ -210,134 +221,18 @@
 Passive・Unique魔法は作戦に設定しなくても発動しますが
 条件を設定した時は条件に一致する場合にのみ効果を発動します。</t>
   </si>
-  <si>
-    <t>◇ゲームの流れ
-「Norm」はステージに配置されたボスを倒すことが目的のシミュレーションRPGです。
-味方ユニットを出撃させバトルを行い敵ユニットを討伐することができます。
-拠点を選択し「出撃」コマンドを選んで味方ユニットを出撃させてみましょう。
-※この内容は「ヘルプ」コマンドで確認することができます。</t>
-    <rPh sb="5" eb="6">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>タオ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>モクテキ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>シュツゲキ</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>キョテン</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>シュツゲキ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>シュツゲキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>味方ユニットの「出撃」「移動」にはコマンドポイントを1消費します。
-コマンドポイントは所有している拠点の数だけ保有し
-「ターン開始」時に最大まで回復します。</t>
-    <rPh sb="0" eb="2">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シュツゲキ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ショユウ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>カズ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ホユウ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>カイシ</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>カイフク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>味方ユニットは拠点とその周りに出撃できます。</t>
-    <rPh sb="0" eb="2">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>キョテン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シュツゲキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>出撃した味方ユニットは「移動」コマンドでマスを移動し
-敵ユニットと接触することでバトルすることができます。</t>
-    <rPh sb="0" eb="2">
-      <t>シュツゲキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ミカタ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>セッショク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,27 +244,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -377,9 +594,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -387,24 +846,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -662,21 +1165,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="5.6328125" customWidth="1"/>
-    <col min="4" max="6" width="7.81640625" customWidth="1"/>
+    <col min="3" max="3" width="5.63636363636364" customWidth="1"/>
+    <col min="4" max="6" width="7.81818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -713,19 +1216,13 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -757,19 +1254,13 @@
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -784,31 +1275,25 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>-472</v>
+        <v>-360</v>
       </c>
       <c r="H3">
-        <v>176</v>
+        <v>-216</v>
       </c>
       <c r="I3">
-        <v>272</v>
+        <v>560</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>-568</v>
       </c>
       <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+        <v>-112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -845,14 +1330,8 @@
       <c r="L4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>1030</v>
       </c>
@@ -889,14 +1368,8 @@
       <c r="L5">
         <v>-160</v>
       </c>
-      <c r="M5">
-        <v>320</v>
-      </c>
-      <c r="N5">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>1040</v>
       </c>
@@ -933,14 +1406,8 @@
       <c r="L6">
         <v>-120</v>
       </c>
-      <c r="M6">
-        <v>720</v>
-      </c>
-      <c r="N6">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>1050</v>
       </c>
@@ -977,14 +1444,8 @@
       <c r="L7">
         <v>-160</v>
       </c>
-      <c r="M7">
-        <v>600</v>
-      </c>
-      <c r="N7">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>1060</v>
       </c>
@@ -1021,14 +1482,8 @@
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>10040</v>
       </c>
@@ -1065,14 +1520,8 @@
       <c r="L9">
         <v>-192</v>
       </c>
-      <c r="M9">
-        <v>360</v>
-      </c>
-      <c r="N9">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>2000</v>
       </c>
@@ -1109,14 +1558,8 @@
       <c r="L10">
         <v>0</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>3000</v>
       </c>
@@ -1153,14 +1596,8 @@
       <c r="L11">
         <v>0</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>3010</v>
       </c>
@@ -1197,14 +1634,8 @@
       <c r="L12">
         <v>-40</v>
       </c>
-      <c r="M12">
-        <v>500</v>
-      </c>
-      <c r="N12">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>3020</v>
       </c>
@@ -1241,14 +1672,8 @@
       <c r="L13">
         <v>-136</v>
       </c>
-      <c r="M13">
-        <v>416</v>
-      </c>
-      <c r="N13">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>4000</v>
       </c>
@@ -1285,14 +1710,8 @@
       <c r="L14">
         <v>16</v>
       </c>
-      <c r="M14">
-        <v>568</v>
-      </c>
-      <c r="N14">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>4010</v>
       </c>
@@ -1329,14 +1748,8 @@
       <c r="L15">
         <v>16</v>
       </c>
-      <c r="M15">
-        <v>600</v>
-      </c>
-      <c r="N15">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>5000</v>
       </c>
@@ -1373,14 +1786,8 @@
       <c r="L16">
         <v>0</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>5010</v>
       </c>
@@ -1417,14 +1824,8 @@
       <c r="L17">
         <v>16</v>
       </c>
-      <c r="M17">
-        <v>572</v>
-      </c>
-      <c r="N17">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>5020</v>
       </c>
@@ -1461,14 +1862,8 @@
       <c r="L18">
         <v>16</v>
       </c>
-      <c r="M18">
-        <v>624</v>
-      </c>
-      <c r="N18">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>6000</v>
       </c>
@@ -1505,14 +1900,8 @@
       <c r="L19">
         <v>104</v>
       </c>
-      <c r="M19">
-        <v>568</v>
-      </c>
-      <c r="N19">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>6010</v>
       </c>
@@ -1549,14 +1938,8 @@
       <c r="L20">
         <v>-144</v>
       </c>
-      <c r="M20">
-        <v>424</v>
-      </c>
-      <c r="N20">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>7000</v>
       </c>
@@ -1593,14 +1976,8 @@
       <c r="L21">
         <v>0</v>
       </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>7010</v>
       </c>
@@ -1637,14 +2014,8 @@
       <c r="L22">
         <v>0</v>
       </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>8000</v>
       </c>
@@ -1681,14 +2052,8 @@
       <c r="L23">
         <v>80</v>
       </c>
-      <c r="M23">
-        <v>480</v>
-      </c>
-      <c r="N23">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>9000</v>
       </c>
@@ -1725,14 +2090,8 @@
       <c r="L24">
         <v>0</v>
       </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>9010</v>
       </c>
@@ -1769,14 +2128,8 @@
       <c r="L25">
         <v>224</v>
       </c>
-      <c r="M25">
-        <v>540</v>
-      </c>
-      <c r="N25">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>10000</v>
       </c>
@@ -1813,14 +2166,8 @@
       <c r="L26">
         <v>208</v>
       </c>
-      <c r="M26">
-        <v>540</v>
-      </c>
-      <c r="N26">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>11000</v>
       </c>
@@ -1857,14 +2204,8 @@
       <c r="L27">
         <v>-160</v>
       </c>
-      <c r="M27">
-        <v>540</v>
-      </c>
-      <c r="N27">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>11010</v>
       </c>
@@ -1901,14 +2242,8 @@
       <c r="L28">
         <v>-136</v>
       </c>
-      <c r="M28">
-        <v>620</v>
-      </c>
-      <c r="N28">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>11020</v>
       </c>
@@ -1945,343 +2280,340 @@
       <c r="L29">
         <v>-56</v>
       </c>
-      <c r="M29">
-        <v>648</v>
-      </c>
-      <c r="N29">
-        <v>144</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="18.81640625" customWidth="1"/>
-    <col min="3" max="3" width="62.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.8181818181818" customWidth="1"/>
+    <col min="3" max="3" width="62.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="117" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" ht="130" spans="1:3">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="39" spans="1:3">
       <c r="A6">
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="26" spans="1:3">
       <c r="A7">
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>10040</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="52" spans="1:3">
       <c r="A10">
         <v>2000</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="26" spans="1:3">
       <c r="A11">
         <v>3000</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="39" spans="1:3">
       <c r="A12">
         <v>3010</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="26" spans="1:3">
       <c r="A13">
         <v>3020</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" ht="26" spans="1:3">
       <c r="A14">
         <v>4000</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" ht="39" spans="1:3">
       <c r="A15">
         <v>4010</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="26" spans="1:3">
       <c r="A16">
         <v>5000</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" ht="26" spans="1:3">
       <c r="A17">
         <v>5010</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" ht="26" spans="1:3">
       <c r="A18">
         <v>5020</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" ht="26" spans="1:3">
       <c r="A19">
         <v>6000</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" ht="52" spans="1:3">
       <c r="A20">
         <v>6010</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" ht="39" spans="1:3">
       <c r="A21">
         <v>7000</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="65" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" ht="65" spans="1:3">
       <c r="A22">
         <v>7010</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" ht="26" spans="1:3">
       <c r="A23">
         <v>8000</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" ht="52" spans="1:3">
       <c r="A24">
         <v>9000</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="26" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" ht="26" spans="1:3">
       <c r="A25">
         <v>9010</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+      <c r="C25" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" ht="39" spans="1:3">
       <c r="A26">
         <v>10000</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="39" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" ht="39" spans="1:3">
       <c r="A27">
         <v>11000</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="65" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" ht="65" spans="1:3">
       <c r="A28">
         <v>11010</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="52" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" ht="52" spans="1:3">
       <c r="A29">
         <v>11020</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="C29" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial" sheetId="3" r:id="rId1"/>
@@ -73,7 +73,14 @@
     <t>課題に記載された内容をこなしてみましょう！</t>
   </si>
   <si>
-    <t>味方ユニットは拠点とその周りに出撃できます。</t>
+    <t>◇ステージ探索
+課題を達成し新たなステージが解放されました！
+メインメニュー画面から「出撃」コマンドでステージを探索することができます。
+ステージに出撃する前に事前に準備ができているか確認しましょう。
+・回復アイテムは用意したか
+・編成に含まれてない仲間がいないか
+・献上できるアイテムが残っていないか
+※この内容は「ヘルプ」コマンドで確認することができます。</t>
   </si>
   <si>
     <t>味方ユニットの「出撃」「移動」にはコマンドポイントを1消費します。
@@ -227,10 +234,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -249,7 +256,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,89 +271,6 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -355,6 +286,38 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -362,7 +325,65 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -377,20 +398,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -401,187 +408,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,11 +602,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,17 +667,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,30 +681,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -700,19 +707,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -721,124 +734,118 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -861,12 +868,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1298,10 +1305,10 @@
         <v>1020</v>
       </c>
       <c r="B4">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>200</v>
@@ -1313,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1040</v>
+        <v>960</v>
       </c>
       <c r="J4">
-        <v>136</v>
+        <v>480</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -1336,10 +1343,10 @@
         <v>1030</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>300</v>
@@ -2330,14 +2337,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" ht="156" spans="1:3">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
@@ -2346,9 +2355,7 @@
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" ht="39" spans="1:3">
       <c r="A6">

--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>バトル</t>
-  </si>
-  <si>
-    <t>■バトル
-バトルは全てオートで進行します。
-バトルは味方か敵全員のHpが0になるか
-150ターンを超えるまで自動で進みます。</t>
   </si>
   <si>
     <t>リザルト</t>
@@ -255,15 +249,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,86 +310,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -385,6 +334,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -408,25 +402,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,157 +570,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,17 +635,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -685,6 +668,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -707,7 +701,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -716,136 +710,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1178,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1343,145 +1337,145 @@
         <v>1030</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>300</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>1040</v>
+        <v>2000</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>4010</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>-280</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>-120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>1050</v>
+        <v>2010</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>-160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>1060</v>
+        <v>2020</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>4040</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>-472</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1492,16 +1486,16 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>10040</v>
+        <v>3000</v>
       </c>
       <c r="B9">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1510,103 +1504,103 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>-272</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>200</v>
+        <v>616</v>
       </c>
       <c r="J9">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="K9">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>-192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>2000</v>
+        <v>3010</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I10">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="J10">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>3000</v>
+        <v>3020</v>
       </c>
       <c r="B11">
         <v>8</v>
       </c>
       <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="I11">
-        <v>616</v>
+        <v>400</v>
       </c>
       <c r="J11">
         <v>112</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>-136</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>3010</v>
+        <v>4000</v>
       </c>
       <c r="B12">
         <v>8</v>
@@ -1615,7 +1609,7 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1624,27 +1618,27 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="I12">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="J12">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="K12">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>-40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>3020</v>
+        <v>4010</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -1653,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1662,39 +1656,39 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>-24</v>
+        <v>176</v>
       </c>
       <c r="I13">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="J13">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="K13">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>-136</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1703,24 +1697,24 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>320</v>
+        <v>540</v>
       </c>
       <c r="J14">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>4010</v>
+        <v>5010</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -1729,28 +1723,28 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-272</v>
       </c>
       <c r="H15">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="I15">
         <v>320</v>
       </c>
       <c r="J15">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="L15">
         <v>16</v>
@@ -1758,16 +1752,16 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>5000</v>
+        <v>5020</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1776,127 +1770,127 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I16">
-        <v>540</v>
+        <v>176</v>
       </c>
       <c r="J16">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
-        <v>5010</v>
+        <v>6000</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>410</v>
+        <v>610</v>
       </c>
       <c r="G17">
-        <v>-272</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>112</v>
+        <v>240</v>
       </c>
       <c r="I17">
-        <v>320</v>
+        <v>1280</v>
       </c>
       <c r="J17">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="K17">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>16</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18">
-        <v>5020</v>
+        <v>6010</v>
       </c>
       <c r="B18">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18">
+        <v>600</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>620</v>
+      </c>
+      <c r="G18">
         <v>500</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>-44</v>
-      </c>
       <c r="H18">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="I18">
-        <v>176</v>
+        <v>280</v>
       </c>
       <c r="J18">
-        <v>72</v>
+        <v>264</v>
       </c>
       <c r="K18">
-        <v>-160</v>
+        <v>400</v>
       </c>
       <c r="L18">
-        <v>16</v>
+        <v>-144</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>1280</v>
+        <v>640</v>
       </c>
       <c r="J19">
         <v>160</v>
@@ -1905,59 +1899,59 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
-        <v>6010</v>
+        <v>7010</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>280</v>
+        <v>720</v>
       </c>
       <c r="J20">
-        <v>264</v>
+        <v>192</v>
       </c>
       <c r="K20">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>-144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="B21">
         <v>8</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1969,33 +1963,33 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="I21">
-        <v>640</v>
+        <v>320</v>
       </c>
       <c r="J21">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22">
-        <v>7010</v>
+        <v>9000</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2010,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>720</v>
+        <v>556</v>
       </c>
       <c r="J22">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -2024,16 +2018,16 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23">
-        <v>8000</v>
+        <v>9010</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2042,112 +2036,112 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H23">
-        <v>216</v>
+        <v>316</v>
       </c>
       <c r="I23">
+        <v>160</v>
+      </c>
+      <c r="J23">
+        <v>64</v>
+      </c>
+      <c r="K23">
         <v>320</v>
       </c>
-      <c r="J23">
-        <v>144</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
       <c r="L23">
-        <v>80</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="B24">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>1100</v>
+      </c>
+      <c r="E24">
         <v>1</v>
       </c>
-      <c r="D24">
-        <v>1000</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="I24">
-        <v>556</v>
+        <v>320</v>
       </c>
       <c r="J24">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25">
-        <v>9010</v>
+        <v>11000</v>
       </c>
       <c r="B25">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>540</v>
+        <v>504</v>
       </c>
       <c r="H25">
-        <v>316</v>
+        <v>-272</v>
       </c>
       <c r="I25">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="J25">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K25">
         <v>320</v>
       </c>
       <c r="L25">
-        <v>224</v>
+        <v>-160</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26">
-        <v>10000</v>
+        <v>11010</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2156,30 +2150,30 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>160</v>
+        <v>504</v>
       </c>
       <c r="H26">
-        <v>320</v>
+        <v>-272</v>
       </c>
       <c r="I26">
-        <v>320</v>
+        <v>184</v>
       </c>
       <c r="J26">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="K26">
         <v>320</v>
       </c>
       <c r="L26">
-        <v>208</v>
+        <v>-136</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27">
-        <v>11000</v>
+        <v>11020</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2194,97 +2188,21 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>-272</v>
+        <v>156</v>
       </c>
       <c r="I27">
-        <v>184</v>
+        <v>1080</v>
       </c>
       <c r="J27">
-        <v>72</v>
+        <v>256</v>
       </c>
       <c r="K27">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28">
-        <v>11010</v>
-      </c>
-      <c r="B28">
-        <v>200</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>1200</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>504</v>
-      </c>
-      <c r="H28">
-        <v>-272</v>
-      </c>
-      <c r="I28">
-        <v>184</v>
-      </c>
-      <c r="J28">
-        <v>72</v>
-      </c>
-      <c r="K28">
-        <v>320</v>
-      </c>
-      <c r="L28">
-        <v>-136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29">
-        <v>11020</v>
-      </c>
-      <c r="B29">
-        <v>111</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>1200</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>156</v>
-      </c>
-      <c r="I29">
-        <v>1080</v>
-      </c>
-      <c r="J29">
-        <v>256</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
         <v>-56</v>
       </c>
     </row>
@@ -2297,7 +2215,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="18.8181818181818" customWidth="1"/>
@@ -2399,224 +2317,240 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" ht="52" spans="1:3">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>2000</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" ht="26" spans="1:3">
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
-        <v>3000</v>
+        <v>2010</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" ht="39" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" ht="26" spans="1:3">
       <c r="A13">
+        <v>3000</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="39" spans="1:3">
+      <c r="A14">
+        <v>3010</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" ht="26" spans="1:3">
+      <c r="A15">
         <v>3020</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" ht="26" spans="1:3">
-      <c r="A14">
-        <v>4000</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="39" spans="1:3">
-      <c r="A15">
-        <v>4010</v>
-      </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" ht="26" spans="1:3">
       <c r="A16">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" ht="26" spans="1:3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" ht="39" spans="1:3">
       <c r="A17">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="26" spans="1:3">
       <c r="A18">
-        <v>5020</v>
+        <v>5000</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:3">
       <c r="A19">
+        <v>5010</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" ht="26" spans="1:3">
+      <c r="A20">
+        <v>5020</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" ht="26" spans="1:3">
+      <c r="A21">
         <v>6000</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="2" t="s">
+    </row>
+    <row r="22" ht="52" spans="1:3">
+      <c r="A22">
+        <v>6010</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" ht="52" spans="1:3">
-      <c r="A20">
-        <v>6010</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="2" t="s">
+    <row r="23" ht="39" spans="1:3">
+      <c r="A23">
+        <v>7000</v>
+      </c>
+      <c r="B23" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" ht="39" spans="1:3">
-      <c r="A21">
-        <v>7000</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="2" t="s">
+    </row>
+    <row r="24" ht="65" spans="1:3">
+      <c r="A24">
+        <v>7010</v>
+      </c>
+      <c r="B24" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" ht="65" spans="1:3">
-      <c r="A22">
-        <v>7010</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C24" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" ht="26" spans="1:3">
-      <c r="A23">
-        <v>8000</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" ht="52" spans="1:3">
-      <c r="A24">
-        <v>9000</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="25" ht="26" spans="1:3">
       <c r="A25">
+        <v>8000</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="52" spans="1:3">
+      <c r="A26">
+        <v>9000</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" ht="26" spans="1:3">
+      <c r="A27">
         <v>9010</v>
       </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" ht="39" spans="1:3">
+      <c r="A28">
+        <v>10000</v>
+      </c>
+      <c r="B28" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" ht="39" spans="1:3">
-      <c r="A26">
-        <v>10000</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="29" ht="39" spans="1:3">
+      <c r="A29">
+        <v>11000</v>
+      </c>
+      <c r="B29" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="27" ht="39" spans="1:3">
-      <c r="A27">
-        <v>11000</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C29" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="30" ht="65" spans="1:3">
+      <c r="A30">
+        <v>11010</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" ht="65" spans="1:3">
-      <c r="A28">
-        <v>11010</v>
-      </c>
-      <c r="B28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    <row r="31" ht="52" spans="1:3">
+      <c r="A31">
+        <v>11020</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="29" ht="52" spans="1:3">
-      <c r="A29">
-        <v>11020</v>
-      </c>
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
   <si>
     <t>Id</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>Help</t>
+  </si>
+  <si>
+    <t>EnglishName</t>
+  </si>
+  <si>
+    <t>EnglishHelp</t>
   </si>
   <si>
     <t>手引き</t>
@@ -228,10 +234,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -249,11 +255,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,36 +308,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -310,10 +330,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -325,16 +346,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -347,23 +376,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -376,22 +398,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -402,13 +408,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,7 +492,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -432,19 +522,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,54 +564,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -511,78 +589,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,6 +599,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -607,6 +624,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,35 +676,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -693,6 +690,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -701,145 +707,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2215,14 +2221,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="18.8181818181818" customWidth="1"/>
     <col min="3" max="3" width="62.8181818181818" customWidth="1"/>
+    <col min="6" max="6" width="14.4636363636364" customWidth="1"/>
+    <col min="7" max="7" width="30.6545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2232,325 +2240,501 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="130" spans="1:3">
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="195" spans="1:7">
       <c r="A2">
         <v>1000</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="26" spans="1:7">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" ht="156" spans="1:3">
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="234" spans="1:7">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1"/>
-    </row>
-    <row r="6" ht="39" spans="1:3">
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" ht="78" spans="1:7">
       <c r="A6">
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" ht="26" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="52" spans="1:7">
       <c r="A7">
         <v>1050</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1060</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>10040</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2000</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2010</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2020</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2"/>
-    </row>
-    <row r="13" ht="26" spans="1:3">
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" ht="39" spans="1:7">
       <c r="A13">
         <v>3000</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" ht="39" spans="1:3">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" ht="65" spans="1:7">
       <c r="A14">
         <v>3010</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" ht="26" spans="1:3">
+      <c r="G14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="39" spans="1:7">
       <c r="A15">
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" ht="26" spans="1:3">
+        <v>27</v>
+      </c>
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="39" spans="1:7">
       <c r="A16">
         <v>4000</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" ht="39" spans="1:3">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="52" spans="1:7">
       <c r="A17">
         <v>4010</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" ht="26" spans="1:3">
+      <c r="G17" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="39" spans="1:7">
       <c r="A18">
         <v>5000</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="26" spans="1:3">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" ht="39" spans="1:7">
       <c r="A19">
         <v>5010</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" ht="26" spans="1:3">
+        <v>34</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" ht="39" spans="1:7">
       <c r="A20">
         <v>5020</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" ht="26" spans="1:3">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" ht="39" spans="1:7">
       <c r="A21">
         <v>6000</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" ht="52" spans="1:3">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" ht="65" spans="1:7">
       <c r="A22">
         <v>6010</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="23" ht="39" spans="1:3">
+      <c r="G22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="78" spans="1:7">
       <c r="A23">
         <v>7000</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="65" spans="1:3">
+        <v>41</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" ht="91" spans="1:7">
       <c r="A24">
         <v>7010</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" ht="26" spans="1:3">
+        <v>43</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" ht="39" spans="1:7">
       <c r="A25">
         <v>8000</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" ht="52" spans="1:3">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" ht="91" spans="1:7">
       <c r="A26">
         <v>9000</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="27" ht="26" spans="1:3">
+      <c r="G26" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" ht="39" spans="1:7">
       <c r="A27">
         <v>9010</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" ht="39" spans="1:3">
+        <v>47</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" ht="78" spans="1:7">
       <c r="A28">
         <v>10000</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" ht="39" spans="1:3">
+        <v>49</v>
+      </c>
+      <c r="F28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" ht="65" spans="1:7">
       <c r="A29">
         <v>11000</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" ht="65" spans="1:3">
+        <v>51</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" ht="104" spans="1:7">
       <c r="A30">
         <v>11010</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" ht="52" spans="1:3">
+      <c r="G30" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" ht="91" spans="1:7">
       <c r="A31">
         <v>11020</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
